--- a/Gestion_Locative_V2_Fidèle.xlsx
+++ b/Gestion_Locative_V2_Fidèle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpas_\Documents\Simulation Corse\Controle financier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8E0602-90CC-4D80-B93A-44D2D0FDF311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02EF51C-A549-4E2A-9EEF-6C9268929DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1005" windowWidth="28065" windowHeight="14925" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="1005" windowWidth="28065" windowHeight="14925" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametrage_Biens" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
   <si>
     <t>Nom du Bien</t>
   </si>
@@ -179,6 +179,15 @@
   </si>
   <si>
     <t>Autre</t>
+  </si>
+  <si>
+    <t>La Zériba</t>
+  </si>
+  <si>
+    <t>Parnassium</t>
+  </si>
+  <si>
+    <t>Océane</t>
   </si>
 </sst>
 </file>
@@ -548,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -573,7 +582,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -587,7 +596,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -596,6 +605,20 @@
         <v>9</v>
       </c>
       <c r="D3">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>0.71</v>
       </c>
     </row>
@@ -637,7 +660,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -657,7 +680,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -677,7 +700,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
